--- a/server/data/reports/salonighode_gmail_com/Selected_Candidates_2026-10-12.xlsx
+++ b/server/data/reports/salonighode_gmail_com/Selected_Candidates_2026-10-12.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>AvaHire AI - Daily Selected Candidates Report (12-Oct-2026)</t>
   </si>
   <si>
-    <t>Selection Date: 12-Oct-2026  |  Total Selected: 2 Selected Candidates  |  Generated: 12/10/2026, 13:19:07</t>
+    <t>Selection Date: 12-Oct-2026  |  Total Selected: 2 Selected Candidates  |  Generated: 12/10/2026, 19:46:51</t>
   </si>
   <si>
     <t>Sr. No.</t>
@@ -58,7 +58,7 @@
     <t>User 1 Selected Candidate</t>
   </si>
   <si>
-    <t>u1.sel.1791791335272@test.com</t>
+    <t>u1.sel.1791814605695@test.com</t>
   </si>
   <si>
     <t>N/A</t>
@@ -70,25 +70,28 @@
     <t>Engineering</t>
   </si>
   <si>
+    <t>12 Oct 2026, 19:46</t>
+  </si>
+  <si>
+    <t>12-Oct-2026</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Selected</t>
+  </si>
+  <si>
+    <t>Download Transcript (.docx)</t>
+  </si>
+  <si>
+    <t>Download Recording (Audio)</t>
+  </si>
+  <si>
+    <t>u1.sel.1791791288048@test.com</t>
+  </si>
+  <si>
     <t>12 Oct 2026, 13:18</t>
-  </si>
-  <si>
-    <t>12-Oct-2026</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Selected</t>
-  </si>
-  <si>
-    <t>Download Transcript (.docx)</t>
-  </si>
-  <si>
-    <t>Download Recording (Audio)</t>
-  </si>
-  <si>
-    <t>u1.sel.1791791288048@test.com</t>
   </si>
 </sst>
 </file>
@@ -745,7 +748,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>20</v>
